--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0009.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0009.xlsx
@@ -2412,7 +2412,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Highest Record: {0}</t>
+          <t>Kỷ Lục Cao Nhất: {0}</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Biến tất cả các khối thành &lt;color=#ecda88&gt;Yellow&lt;/color&gt; đi</t>
+          <t>Biến tất cả các khối thành &lt;color=#ecda88&gt;Vàng&lt;/color&gt; đi</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Biến tất cả các khối thành &lt;color=#bc5044&gt;Red&lt;/color&gt; đi</t>
+          <t>Biến tất cả các khối thành &lt;color=#bc5044&gt;Đỏ&lt;/color&gt; đi</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Biến tất cả các khối thành &lt;color=#54a891&gt;Green&lt;/color&gt; đi</t>
+          <t>Biến tất cả các khối thành &lt;color=#54a891&gt;Xanh Lá&lt;/color&gt; đi</t>
         </is>
       </c>
     </row>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Biến tất cả các khối thành &lt;color=#5081bc&gt;Blue&lt;/color&gt; đi</t>
+          <t>Biến tất cả các khối thành &lt;color=#5081bc&gt;Xanh Dương&lt;/color&gt; đi</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Sau khi duy trì trên không hơn {0} giây, Cộng Hưởng Giả thực hiện Tấn Công Đâm Xuống và tiếp đất, tạo ra một khối băng nhỏ khi chạm đất.</t>
+          <t>Sau khi duy trì trên không hơn {0} giây, Resonator thực hiện Tấn Công Đâm Xuống và tiếp đất, tạo ra một khối băng nhỏ khi chạm đất.</t>
         </is>
       </c>
     </row>
@@ -5987,7 +5987,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Sau khi duy trì trên không hơn {0} giây, Cộng Hưởng Giả thực hiện Tấn Công Đâm Xuống và tiếp đất, tạo ra một khối băng trung bình khi chạm đất.</t>
+          <t>Sau khi duy trì trên không hơn {0} giây, Resonator thực hiện Tấn Công Đâm Xuống và tiếp đất, tạo ra một khối băng trung bình khi chạm đất.</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Sau khi duy trì trên không hơn {0} giây, Cộng Hưởng Giả thực hiện Tấn Công Đâm Xuống và tiếp đất, tạo ra một khối băng lớn khi chạm đất.</t>
+          <t>Sau khi duy trì trên không hơn {0} giây, Resonator thực hiện Tấn Công Đâm Xuống và tiếp đất, tạo ra một khối băng lớn khi chạm đất.</t>
         </is>
       </c>
     </row>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Tất cả Cộng Hưởng Giả trong đội nhận được một lần hồi sinh mỗi {0} giây, tối đa &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=1}.</t>
+          <t>Tất cả Resonator trong đội nhận được một lần hồi sinh mỗi {0} giây, tối đa &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=1}.</t>
         </is>
       </c>
     </row>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Trở thành người &lt;color=Highlight&gt;Become the last one to move&lt;/color&gt; trong lượt tiếp theo.</t>
+          <t>Trở thành người &lt;color=Highlight&gt;di chuyển cuối cùng&lt;/color&gt; trong lượt tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Khi đứng cuối bảng, &lt;color=Highlight&gt;advance 3 extra pads&lt;/color&gt;.</t>
+          <t>Khi đứng cuối bảng, &lt;color=Highlight&gt;tiến thêm 3 ô&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Xúc xắc &lt;color=Highlight&gt;only roll a 2 or 3&lt;/color&gt;.</t>
+          <t>Xúc xắc &lt;color=Highlight&gt;chỉ có thể ra 2 hoặc 3&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9432,7 +9432,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Di chuyển riêng biệt và tiến thêm số bậc bằng với số Cube khác trên bậc đó.</t>
+          <t>Di chuy?n ri?ng bi?t v? ti?n th?m s? ? b?ng v?i s? Cube kh?c tr?n ? ??.</t>
         </is>
       </c>
     </row>
@@ -9497,7 +9497,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Tiến &lt;color=Highlight&gt;Advance twice&lt;/color&gt; với số đã tung.</t>
+          <t>Tiến &lt;color=Highlight&gt;hai lượt&lt;/color&gt; với số đã tung.</t>
         </is>
       </c>
     </row>
@@ -9562,7 +9562,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Đi thêm &lt;color=Highlight&gt;Advance 2 extra pads&lt;/color&gt; vì là người di chuyển cuối cùng.</t>
+          <t>Đi thêm &lt;color=Highlight&gt;2 ô&lt;/color&gt; vì là người di chuyển cuối cùng.</t>
         </is>
       </c>
     </row>
@@ -9627,7 +9627,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Đi thêm &lt;color=Highlight&gt;Advance 2 extra pads&lt;/color&gt; vì là người di chuyển đầu tiên.</t>
+          <t>Đi thêm &lt;color=Highlight&gt;2 ô&lt;/color&gt; vì là người di chuyển đầu tiên.</t>
         </is>
       </c>
     </row>
@@ -9692,7 +9692,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Xúc xắc chỉ có thể ra 1 hoặc 3, và sẽ tiến thêm &lt;color=Highlight&gt;2 extra pads&lt;/color&gt; trong lượt này.</t>
+          <t>Xúc xắc chỉ có thể ra 1 hoặc 3, và sẽ tiến thêm &lt;color=Highlight&gt;2 ô&lt;/color&gt; trong lượt này.</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Di chuyển thêm &lt;color=Highlight&gt;2 extra pads&lt;/color&gt; trong lượt này.</t>
+          <t>Di chuyển thêm &lt;color=Highlight&gt;2 ô&lt;/color&gt; trong lượt này.</t>
         </is>
       </c>
     </row>
@@ -9822,7 +9822,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Di chuyển thêm &lt;color=Highlight&gt;1 extra pad&lt;/color&gt; trong lượt này.</t>
+          <t>Di chuyển thêm &lt;color=Highlight&gt;1 ô&lt;/color&gt; trong lượt này.</t>
         </is>
       </c>
     </row>
@@ -12617,7 +12617,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Jinhsi biết ơn vận may đã đưa cô đến trận chung kết. Giờ đây, cô đã sẵn sàng hợp sức cùng các Cộng Hưởng Giả khác để giành lấy chiến thắng cuối cùng!</t>
+          <t>Jinhsi biết ơn vận may đã đưa cô đến trận chung kết. Giờ đây, cô đã sẵn sàng hợp sức cùng các Resonator khác để giành lấy chiến thắng cuối cùng!</t>
         </is>
       </c>
     </row>
@@ -16127,7 +16127,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để đóng</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để đóng.</t>
         </is>
       </c>
     </row>
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Một con đường dài vắt ngang miền nam Lahai-Roi. Đầu kia của nó nối thẳng về quê hương của người Roya: rừng Bjartr.</t>
+          <t>Một con đường dài vắt ngang miền nam Lahai-Roi. Đầu kia của nó nối thẳng về quê hương của người Roya: Bjartr Woods.</t>
         </is>
       </c>
     </row>
@@ -21073,7 +21073,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Cậu tình cờ nghe được truyền thuyết đô thị về "Miko Ma Ám Yêu Film" trong nhóm chat của Học Viện. Cậu quyết định đến phòng chiếu phim để xem sao.</t>
+          <t>Cậu tình cờ nghe được truyền thuyết đô thị về "Miko Ma Ám Yêu Phim" trong nhóm chat của Học Viện. Cậu quyết định đến phòng chiếu phim để xem sao.</t>
         </is>
       </c>
     </row>
@@ -22439,7 +22439,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Gửi Rover:
+          <t>Gửi Vận Mệnh Giả:
 Phần thưởng đăng nhập KU Block đã được gửi đi, vui lòng kiểm tra trong file đính kèm.</t>
         </is>
       </c>
@@ -22637,7 +22637,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Rover thân mến, sự kiện {0} sắp kết thúc. Đừng ngần ngại tham gia và nhận phần thưởng sự kiện của bạn nhé. Cảm ơn vì đã ủng hộ!</t>
+          <t>Vận Mệnh Giả thân mến, sự kiện {0} sắp kết thúc. Đừng ngần ngại tham gia và nhận phần thưởng sự kiện của bạn nhé. Cảm ơn vì đã ủng hộ!</t>
         </is>
       </c>
     </row>
@@ -22702,7 +22702,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Rover thân mến, phần thưởng giới hạn thời gian của Somnium Labyrinth sắp hết hạn. Đừng ngần ngại tham gia và nhận phần thưởng sự kiện của bạn nhé. Cảm ơn vì đã ủng hộ!</t>
+          <t>Vận Mệnh Giả thân mến, phần thưởng giới hạn thời gian của Somnium Labyrinth sắp hết hạn. Đừng ngần ngại tham gia và nhận phần thưởng sự kiện của bạn nhé. Cảm ơn vì đã ủng hộ!</t>
         </is>
       </c>
     </row>
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Mới ra lò từ Trụ sở Lollo Logistics, người bạn cũ Maji quyết định khởi động lại Chiến dịch Lollo. Có vẻ cậu lại cần đến sự giúp đỡ của cậu lần nữa rồi.</t>
+          <t>Mới ra lò từ Trụ sở Lollo Logistics, người bạn cũ Maji quyết định khởi động lại Chiến dịch Lollo. Có vẻ cậu lại cần đến sự giúp đỡ của mày lần nữa rồi.</t>
         </is>
       </c>
     </row>
@@ -24264,7 +24264,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Huaxu Academy vừa đạt được bước đột phá trong công nghệ Công cụ. Nhà nghiên cứu Lanyan hiện đang cần sự hỗ trợ của cậu để thử nghiệm một công cụ mới gần Học viện.</t>
+          <t>Học viện Huaxu vừa đạt được bước đột phá trong công nghệ Utility. Nhà nghiên cứu Lanyan hiện đang cần sự hỗ trợ của cậu để thử nghiệm một công cụ mới gần Học viện.</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Rover thân mến, sự kiện {0} sắp kết thúc. Đừng ngần ngại tham gia và nhận phần thưởng sự kiện của bạn nhé. Cảm ơn vì đã ủng hộ!</t>
+          <t>Vận Mệnh Giả thân mến, sự kiện {0} sắp kết thúc. Đừng ngần ngại tham gia và nhận phần thưởng sự kiện của bạn nhé. Cảm ơn vì đã ủng hộ!</t>
         </is>
       </c>
     </row>
@@ -24459,7 +24459,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Rover thân mến, sự kiện {0} sắp kết thúc. Đừng ngần ngại tham gia và nhận phần thưởng sự kiện của bạn nhé. Cảm ơn vì đã ủng hộ!</t>
+          <t>Vận Mệnh Giả thân mến, sự kiện {0} sắp kết thúc. Đừng ngần ngại tham gia và nhận phần thưởng sự kiện của bạn nhé. Cảm ơn vì đã ủng hộ!</t>
         </is>
       </c>
     </row>
@@ -24524,7 +24524,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Rover thân mến, sự kiện Freeze Frame: Action Highlights sắp kết thúc. Đừng ngần ngại tham gia và nhận phần thưởng sự kiện của bạn nhé. Cảm ơn vì đã ủng hộ!</t>
+          <t>Vận Mệnh Giả thân mến, sự kiện Freeze Frame: Action Highlights sắp kết thúc. Đừng ngần ngại tham gia và nhận phần thưởng sự kiện của bạn nhé. Cảm ơn vì đã ủng hộ!</t>
         </is>
       </c>
     </row>
@@ -24784,7 +24784,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Xung quanh một Quả Cầu Sonoro, cậu tình cờ gặp một nhà nghiên cứu đang gặp rắc rối, dường như hắn có việc quan trọng cần làm...</t>
+          <t>Xung quanh một Sonoro Sphere, cậu tình cờ gặp một nhà nghiên cứu đang gặp rắc rối, dường như hắn có việc quan trọng cần làm...</t>
         </is>
       </c>
     </row>
@@ -31349,7 +31349,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Dù chỉ đi ngang qua hay định gọi nơi này là nhà, chúng tôi hy vọng cậu sẽ có khoảng thời gian vui vẻ ở Kim Châu.</t>
+          <t>Dù chỉ đi ngang qua hay định gọi nơi này là nhà, chúng tôi hy vọng cậu sẽ có khoảng thời gian vui vẻ ở Jinzhou.</t>
         </is>
       </c>
     </row>
@@ -32909,7 +32909,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Đừng bảo là chỉ vì do chính tay ta pha đấy chứ?</t>
+          <t>Đừng bảo là chỉ vì do chính tay tao pha đấy chứ?</t>
         </is>
       </c>
     </row>
@@ -32974,7 +32974,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Hừ... Có lẽ cậu nói đúng.</t>
+          <t>Hừ... Có lẽ mày nói đúng.</t>
         </is>
       </c>
     </row>
